--- a/bakup/customers.xlsx
+++ b/bakup/customers.xlsx
@@ -1,92 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="14">
-  <si>
-    <t>کد</t>
-  </si>
-  <si>
-    <t>نام</t>
-  </si>
-  <si>
-    <t>جمع حساب</t>
-  </si>
-  <si>
-    <t>تاریخ</t>
-  </si>
-  <si>
-    <t>دانیال ابراهیمی</t>
-  </si>
-  <si>
-    <t>محمد حسین رحمتی</t>
-  </si>
-  <si>
-    <t>عباس رحمتی</t>
-  </si>
-  <si>
-    <t>محمد صالح رحمتی</t>
-  </si>
-  <si>
-    <t>امیر مهدی رحمتی</t>
-  </si>
-  <si>
-    <t>رضا میرزائی</t>
-  </si>
-  <si>
-    <t>محمد جواد میرزایی</t>
-  </si>
-  <si>
-    <t>بوفون</t>
-  </si>
-  <si>
-    <t>علیرضا رحمتی</t>
-  </si>
-  <si>
-    <t>1405/04/08</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="18"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -105,30 +54,89 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -394,162 +402,283 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D14"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="12.75" customWidth="1"/>
-    <col min="2" max="2" width="13.125" customWidth="1"/>
-    <col min="3" max="3" width="11.25" customWidth="1"/>
-    <col min="4" max="4" width="13.5" customWidth="1"/>
+    <col width="12.75" customWidth="1" min="1" max="1"/>
+    <col width="13.125" customWidth="1" min="2" max="2"/>
+    <col width="11.25" customWidth="1" min="3" max="3"/>
+    <col width="13.5" customWidth="1" min="4" max="4"/>
+    <col width="22.625" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="2">
-        <v>9012</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="3">
-        <v>1036000</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="2">
+    <row r="1" ht="29.25" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>کد</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>نام</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>جمع حساب</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>تاریخ</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>نام فایل</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="29.25" customHeight="1">
+      <c r="A2" s="3" t="n">
+        <v>1786</v>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>دانیال ابراهیمی</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>2315000</v>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>1405/05/26</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>danial.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="29.25" customHeight="1">
+      <c r="A3" s="3" t="n">
         <v>2243</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="3">
-        <v>3637000</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="2">
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>محمد حسین رحمتی</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>5379000</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>1405/05/26</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>mohammad hosein.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="29.25" customHeight="1">
+      <c r="A4" s="3" t="n">
         <v>4322</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="3">
-        <v>2134000</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="2">
-        <v>3422</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="3">
-        <v>-62000</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="2">
-        <v>5022</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="3">
-        <v>0</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="2">
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>عباس رحمتی</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>3292000</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>1405/05/26</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>abas.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="29.25" customHeight="1">
+      <c r="A5" s="3" t="n">
+        <v>3596</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>محمد صالح رحمتی</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>208000</v>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>1405/05/26</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>mohammad saleh.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="29.25" customHeight="1">
+      <c r="A6" s="3" t="n">
+        <v>9950</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>امیر مهدی رحمتی</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>85000</v>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>1405/04/19</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>amir mahdi.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="29.25" customHeight="1">
+      <c r="A7" s="3" t="n">
         <v>2205</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="3">
-        <v>3340000</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="2">
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>رضا میرزائی</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>3475000</v>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>1405/04/18</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>reza.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="29.25" customHeight="1">
+      <c r="A8" s="3" t="n">
         <v>2250</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="3">
-        <v>351500</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="2">
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>محمد جواد میرزایی</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>646500</v>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>1405/05/02</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>mohammad javad.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="29.25" customHeight="1">
+      <c r="A9" s="3" t="n">
         <v>6090</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="3">
-        <v>1322600</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="2">
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>بوفون</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>2514600</v>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>1405/05/18</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>bofon.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="29.25" customHeight="1">
+      <c r="A10" s="3" t="n">
         <v>195</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="3">
-        <v>10450000</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="12" spans="1:4" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="13" spans="1:4" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="14" spans="1:4" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>علیرضا رحمتی</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>6450000</v>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>1405/04/19</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>alireza.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="29.25" customHeight="1">
+      <c r="A11" s="3" t="n">
+        <v>9906</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>امیر رضا رحمتی</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>366000</v>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>1405/04/24</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>amir reza.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="29.25" customHeight="1"/>
+    <row r="13" ht="29.25" customHeight="1"/>
+    <row r="14" ht="29.25" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup orientation="portrait" paperSize="9" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/bakup/customers.xlsx
+++ b/bakup/customers.xlsx
@@ -407,8 +407,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25" outlineLevelCol="0"/>
+  <dimension ref="A1:E27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="12.75" customWidth="1" min="1" max="1"/>
     <col width="13.125" customWidth="1" min="2" max="2"/>
@@ -454,11 +454,11 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>2315000</v>
+        <v>2575000</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>1405/05/26</t>
+          <t>1405/06/02 - 19:41</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -477,11 +477,11 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>5379000</v>
+        <v>5639000</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>1405/05/26</t>
+          <t>1405/06/02 - 19:41</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -500,11 +500,11 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>3292000</v>
+        <v>3677000</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>1405/05/26</t>
+          <t>1405/06/05 - 15:34</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -523,11 +523,11 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>208000</v>
+        <v>518000</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>1405/05/26</t>
+          <t>1405/06/02 - 19:42</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -546,11 +546,11 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>85000</v>
+        <v>220000</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>1405/04/19</t>
+          <t>1405/06/05 - 15:35</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -569,11 +569,11 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>3475000</v>
+        <v>3610000</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>1405/04/18</t>
+          <t>1405/06/05 - 15:38</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -592,11 +592,11 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>646500</v>
+        <v>866500</v>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>1405/05/02</t>
+          <t>1405/06/01 - 16:49</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -615,11 +615,11 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>2514600</v>
+        <v>2924600</v>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>1405/05/18</t>
+          <t>1405/06/05 - 15:37</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>1405/04/19</t>
+          <t>1405/04/19 - 19:43</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>1405/04/24</t>
+          <t>1405/04/24 - 18:53</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -674,9 +674,182 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="29.25" customHeight="1"/>
-    <row r="13" ht="29.25" customHeight="1"/>
-    <row r="14" ht="29.25" customHeight="1"/>
+    <row r="12" ht="29.25" customHeight="1">
+      <c r="A12" s="3" t="n">
+        <v>1234</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>مرتضی شمسی</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>1405/06/04 - 18:38</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>morteza shamsi.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="29.25" customHeight="1">
+      <c r="A13" s="3" t="n">
+        <v>9159</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>سبحان ترابی</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>1437000</v>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>1405/05/31 - 16:56</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>sobhan.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="29.25" customHeight="1">
+      <c r="A14" s="3" t="n">
+        <v>8106</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>امیر حسین رحمتی</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>4891000</v>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>1405/05/31 - 16:57</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>amir hosein.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="27.75" customHeight="1">
+      <c r="A15" s="3" t="n">
+        <v>3238</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>متین میرزائی</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>425000</v>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>1405/06/02 - 11:28</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>matin.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="27.75" customHeight="1">
+      <c r="A16" s="3" t="n"/>
+      <c r="B16" s="3" t="n"/>
+      <c r="C16" s="2" t="n"/>
+      <c r="D16" s="3" t="n"/>
+      <c r="E16" s="3" t="n"/>
+    </row>
+    <row r="17" ht="27.75" customHeight="1">
+      <c r="A17" s="3" t="n"/>
+      <c r="B17" s="3" t="n"/>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="3" t="n"/>
+      <c r="E17" s="3" t="n"/>
+    </row>
+    <row r="18" ht="27.75" customHeight="1">
+      <c r="A18" s="3" t="n"/>
+      <c r="B18" s="3" t="n"/>
+      <c r="C18" s="2" t="n"/>
+      <c r="D18" s="3" t="n"/>
+      <c r="E18" s="3" t="n"/>
+    </row>
+    <row r="19" ht="27.75" customHeight="1">
+      <c r="A19" s="3" t="n"/>
+      <c r="B19" s="3" t="n"/>
+      <c r="C19" s="2" t="n"/>
+      <c r="D19" s="3" t="n"/>
+      <c r="E19" s="3" t="n"/>
+    </row>
+    <row r="20" ht="27.75" customHeight="1">
+      <c r="A20" s="3" t="n"/>
+      <c r="B20" s="3" t="n"/>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="3" t="n"/>
+      <c r="E20" s="3" t="n"/>
+    </row>
+    <row r="21" ht="27.75" customHeight="1">
+      <c r="A21" s="3" t="n"/>
+      <c r="B21" s="3" t="n"/>
+      <c r="C21" s="3" t="n"/>
+      <c r="D21" s="3" t="n"/>
+      <c r="E21" s="3" t="n"/>
+    </row>
+    <row r="22" ht="27.75" customHeight="1">
+      <c r="A22" s="3" t="n"/>
+      <c r="B22" s="3" t="n"/>
+      <c r="C22" s="3" t="n"/>
+      <c r="D22" s="3" t="n"/>
+      <c r="E22" s="3" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n"/>
+      <c r="B23" s="3" t="n"/>
+      <c r="C23" s="3" t="n"/>
+      <c r="D23" s="3" t="n"/>
+      <c r="E23" s="3" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="n"/>
+      <c r="B24" s="3" t="n"/>
+      <c r="C24" s="3" t="n"/>
+      <c r="D24" s="3" t="n"/>
+      <c r="E24" s="3" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n"/>
+      <c r="B25" s="3" t="n"/>
+      <c r="C25" s="3" t="n"/>
+      <c r="D25" s="3" t="n"/>
+      <c r="E25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="n"/>
+      <c r="B26" s="3" t="n"/>
+      <c r="C26" s="3" t="n"/>
+      <c r="D26" s="3" t="n"/>
+      <c r="E26" s="3" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n"/>
+      <c r="B27" s="3" t="n"/>
+      <c r="C27" s="3" t="n"/>
+      <c r="D27" s="3" t="n"/>
+      <c r="E27" s="3" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" verticalDpi="0"/>
